--- a/dataset_t6_grouped/results2/G3/G3_T1829_W0042F0002T0006Z000C1N17_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T1829_W0042F0002T0006Z000C1N17_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>34.51353135532833</v>
+        <v>5.608448845240853</v>
       </c>
       <c r="D2" t="n">
-        <v>58.55064337216395</v>
+        <v>9.514479547976643</v>
       </c>
       <c r="E2" t="n">
-        <v>14.31610081086455</v>
+        <v>2.326366381765489</v>
       </c>
       <c r="F2" t="n">
-        <v>18.44230441669912</v>
+        <v>2.996874467713607</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>57.65269348112658</v>
+        <v>9.368562690683071</v>
       </c>
       <c r="D3" t="n">
-        <v>60.04679184685763</v>
+        <v>9.757603675114366</v>
       </c>
       <c r="E3" t="n">
-        <v>14.31610081086455</v>
+        <v>2.326366381765489</v>
       </c>
       <c r="F3" t="n">
-        <v>18.44230441669912</v>
+        <v>2.996874467713607</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>21.50841633506823</v>
+        <v>3.495117654448588</v>
       </c>
       <c r="D4" t="n">
-        <v>22.04883260200314</v>
+        <v>3.58293529782551</v>
       </c>
       <c r="E4" t="n">
-        <v>14.31610081086455</v>
+        <v>2.326366381765489</v>
       </c>
       <c r="F4" t="n">
-        <v>18.44230441669912</v>
+        <v>2.996874467713607</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>23.77384661274739</v>
+        <v>3.863250074571451</v>
       </c>
       <c r="D5" t="n">
-        <v>22.81775374626175</v>
+        <v>3.707884983767535</v>
       </c>
       <c r="E5" t="n">
-        <v>14.31610081086455</v>
+        <v>2.326366381765489</v>
       </c>
       <c r="F5" t="n">
-        <v>18.44230441669912</v>
+        <v>2.996874467713607</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
